--- a/data/derived_data/6_NMI_CCA/Dataset_1/CCA_NULL_ITS_D1_04.xlsx
+++ b/data/derived_data/6_NMI_CCA/Dataset_1/CCA_NULL_ITS_D1_04.xlsx
@@ -427,10 +427,10 @@
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.538286356209151</v>
+        <v>0.538286356209148</v>
       </c>
       <c r="D3" t="n">
-        <v>4.50941525971249</v>
+        <v>4.50941525971246</v>
       </c>
       <c r="E3" t="n">
         <v>0.0001</v>
